--- a/data_lake/macro/USA/FED Target Rate.xlsx
+++ b/data_lake/macro/USA/FED Target Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95144205-8C2F-4856-A103-5F9094F7BF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9823834-A5F1-4581-A1B9-8A87B217AB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fed Target Rate" sheetId="1" r:id="rId1"/>
@@ -73,28 +73,28 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -102,7 +102,7 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -110,9 +110,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -141,29 +146,29 @@
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="백분율" xfId="1" builtinId="5"/>
@@ -221,7 +226,7 @@
               <a:solidFill>
                 <a:schemeClr val="accent5"/>
               </a:solidFill>
-              <a:prstDash val="dash"/>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -232,7 +237,19 @@
           <c:dPt>
             <c:idx val="266"/>
             <c:marker>
-              <c:symbol val="none"/>
+              <c:symbol val="circle"/>
+              <c:size val="5"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="accent1"/>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
             </c:marker>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -240,7 +257,7 @@
                 <a:solidFill>
                   <a:schemeClr val="accent5"/>
                 </a:solidFill>
-                <a:prstDash val="dash"/>
+                <a:prstDash val="solid"/>
                 <a:round/>
               </a:ln>
               <a:effectLst/>
@@ -2088,6 +2105,9 @@
                   <c:v>3.7499999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="297">
+                  <c:v>3.7499999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="298">
                   <c:v>3.7499999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
@@ -2117,7 +2137,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="46387"/>
-          <c:min val="36526"/>
+          <c:min val="40179"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -3133,17 +3153,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G311"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" style="9" customWidth="1"/>
-    <col min="5" max="7" width="9.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.59765625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.8984375" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.3984375" style="10" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -3166,7 +3188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>30221</v>
       </c>
@@ -3199,7 +3221,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>30225</v>
       </c>
@@ -3235,7 +3257,7 @@
         <v>0.10249999999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="7">
         <v>30231</v>
       </c>
@@ -3256,7 +3278,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>30274</v>
       </c>
@@ -3277,7 +3299,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
         <v>30299</v>
       </c>
@@ -3298,7 +3320,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
         <v>30406</v>
       </c>
@@ -3319,7 +3341,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>30461</v>
       </c>
@@ -3340,7 +3362,7 @@
         <v>8.6199999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
         <v>30491</v>
       </c>
@@ -3361,7 +3383,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="7">
         <v>30511</v>
       </c>
@@ -3382,7 +3404,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>30517</v>
       </c>
@@ -3403,7 +3425,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>30539</v>
       </c>
@@ -3424,7 +3446,7 @@
         <v>9.4299999999999995E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>30545</v>
       </c>
@@ -3445,7 +3467,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>30574</v>
       </c>
@@ -3466,7 +3488,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
         <v>30770</v>
       </c>
@@ -3487,7 +3509,7 @@
         <v>9.3700000000000006E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>30868</v>
       </c>
@@ -3508,7 +3530,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>30882</v>
       </c>
@@ -3529,7 +3551,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>30903</v>
       </c>
@@ -3550,7 +3572,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>30945</v>
       </c>
@@ -3571,7 +3593,7 @@
         <v>0.115</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>30952</v>
       </c>
@@ -3592,7 +3614,7 @@
         <v>0.1125</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>30966</v>
       </c>
@@ -3613,7 +3635,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="7">
         <v>30973</v>
       </c>
@@ -3634,7 +3656,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="7">
         <v>30994</v>
       </c>
@@ -3655,7 +3677,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
         <v>31009</v>
       </c>
@@ -3676,7 +3698,7 @@
         <v>9.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>31022</v>
       </c>
@@ -3697,7 +3719,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>31035</v>
       </c>
@@ -3718,7 +3740,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="7">
         <v>31040</v>
       </c>
@@ -3739,7 +3761,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="7">
         <v>31071</v>
       </c>
@@ -3760,7 +3782,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="7">
         <v>31092</v>
       </c>
@@ -3781,7 +3803,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="7">
         <v>31134</v>
       </c>
@@ -3802,7 +3824,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="7">
         <v>31162</v>
       </c>
@@ -3823,7 +3845,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>31187</v>
       </c>
@@ -3844,7 +3866,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>31239</v>
       </c>
@@ -3865,7 +3887,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>31253</v>
       </c>
@@ -3886,7 +3908,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>31280</v>
       </c>
@@ -3907,7 +3929,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>31296</v>
       </c>
@@ -3928,7 +3950,7 @@
         <v>7.8100000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
         <v>31399</v>
       </c>
@@ -3949,7 +3971,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>31478</v>
       </c>
@@ -3970,7 +3992,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="7">
         <v>31504</v>
       </c>
@@ -3991,7 +4013,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>31523</v>
       </c>
@@ -4012,7 +4034,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
         <v>31554</v>
       </c>
@@ -4033,7 +4055,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="7">
         <v>31568</v>
       </c>
@@ -4054,7 +4076,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="7">
         <v>31604</v>
       </c>
@@ -4075,7 +4097,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="7">
         <v>31645</v>
       </c>
@@ -4096,7 +4118,7 @@
         <v>6.3700000000000007E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
         <v>31782</v>
       </c>
@@ -4117,7 +4139,7 @@
         <v>5.8700000000000002E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
         <v>31897</v>
       </c>
@@ -4138,7 +4160,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
         <v>31919</v>
       </c>
@@ -4159,7 +4181,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="7">
         <v>31960</v>
       </c>
@@ -4180,7 +4202,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="7">
         <v>32016</v>
       </c>
@@ -4201,7 +4223,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
         <v>32023</v>
       </c>
@@ -4222,7 +4244,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
         <v>32024</v>
       </c>
@@ -4243,7 +4265,7 @@
         <v>6.8699999999999997E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
         <v>32044</v>
       </c>
@@ -4264,7 +4286,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="7">
         <v>32085</v>
       </c>
@@ -4285,7 +4307,7 @@
         <v>7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="7">
         <v>32170</v>
       </c>
@@ -4306,7 +4328,7 @@
         <v>6.8099999999999994E-2</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
         <v>32184</v>
       </c>
@@ -4327,7 +4349,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="7">
         <v>32232</v>
       </c>
@@ -4348,7 +4370,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="7">
         <v>32272</v>
       </c>
@@ -4369,7 +4391,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
         <v>32288</v>
       </c>
@@ -4390,7 +4412,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
         <v>32316</v>
       </c>
@@ -4411,7 +4433,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
         <v>32325</v>
       </c>
@@ -4432,7 +4454,7 @@
         <v>7.4300000000000005E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="7">
         <v>32343</v>
       </c>
@@ -4453,7 +4475,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="7">
         <v>32363</v>
       </c>
@@ -4474,7 +4496,7 @@
         <v>7.6799999999999993E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="7">
         <v>32364</v>
       </c>
@@ -4495,7 +4517,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="7">
         <v>32464</v>
       </c>
@@ -4516,7 +4538,7 @@
         <v>8.1199999999999994E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="7">
         <v>32469</v>
       </c>
@@ -4537,7 +4559,7 @@
         <v>8.3099999999999993E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
         <v>32492</v>
       </c>
@@ -4558,7 +4580,7 @@
         <v>8.3699999999999997E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="7">
         <v>32513</v>
       </c>
@@ -4594,7 +4616,7 @@
         <v>8.6800000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="7">
         <v>32548</v>
       </c>
@@ -4615,7 +4637,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="7">
         <v>32553</v>
       </c>
@@ -4636,7 +4658,7 @@
         <v>9.1200000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="7">
         <v>32563</v>
       </c>
@@ -4657,7 +4679,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
         <v>32645</v>
       </c>
@@ -4678,7 +4700,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
         <v>32665</v>
       </c>
@@ -4699,7 +4721,7 @@
         <v>9.8100000000000007E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
         <v>32696</v>
       </c>
@@ -4720,7 +4742,7 @@
         <v>9.5600000000000004E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="7">
         <v>32716</v>
       </c>
@@ -4741,7 +4763,7 @@
         <v>9.3100000000000002E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="7">
         <v>32800</v>
       </c>
@@ -4762,7 +4784,7 @@
         <v>9.06E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
         <v>32818</v>
       </c>
@@ -4783,7 +4805,7 @@
         <v>8.7499999999999994E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
         <v>32862</v>
       </c>
@@ -4804,7 +4826,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="7">
         <v>33067</v>
       </c>
@@ -4825,7 +4847,7 @@
         <v>8.2500000000000004E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="7">
         <v>33175</v>
       </c>
@@ -4846,7 +4868,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
         <v>33191</v>
       </c>
@@ -4867,7 +4889,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
         <v>33214</v>
       </c>
@@ -4888,7 +4910,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
         <v>33226</v>
       </c>
@@ -4909,7 +4931,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" s="7">
         <v>33247</v>
       </c>
@@ -4930,7 +4952,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
         <v>33270</v>
       </c>
@@ -4951,7 +4973,7 @@
         <v>6.7500000000000004E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
         <v>33305</v>
       </c>
@@ -4972,7 +4994,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" s="7">
         <v>33358</v>
       </c>
@@ -4993,7 +5015,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="7">
         <v>33456</v>
       </c>
@@ -5014,7 +5036,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
         <v>33494</v>
       </c>
@@ -5035,7 +5057,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
         <v>33542</v>
       </c>
@@ -5056,7 +5078,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
         <v>33548</v>
       </c>
@@ -5077,7 +5099,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="7">
         <v>33578</v>
       </c>
@@ -5098,7 +5120,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" s="7">
         <v>33592</v>
       </c>
@@ -5119,7 +5141,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
         <v>33703</v>
       </c>
@@ -5140,7 +5162,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
         <v>33787</v>
       </c>
@@ -5161,7 +5183,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
         <v>33851</v>
       </c>
@@ -5182,7 +5204,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" s="7">
         <v>34369</v>
       </c>
@@ -5203,7 +5225,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" s="7">
         <v>34415</v>
       </c>
@@ -5224,7 +5246,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" s="7">
         <v>34442</v>
       </c>
@@ -5245,7 +5267,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
         <v>34471</v>
       </c>
@@ -5266,7 +5288,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" s="7">
         <v>34562</v>
       </c>
@@ -5287,7 +5309,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" s="7">
         <v>34653</v>
       </c>
@@ -5308,7 +5330,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
         <v>34731</v>
       </c>
@@ -5329,7 +5351,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
         <v>34886</v>
       </c>
@@ -5350,7 +5372,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
         <v>35052</v>
       </c>
@@ -5371,7 +5393,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" s="7">
         <v>35095</v>
       </c>
@@ -5392,7 +5414,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
         <v>35514</v>
       </c>
@@ -5413,7 +5435,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
         <v>36067</v>
       </c>
@@ -5434,7 +5456,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" s="7">
         <v>36083</v>
       </c>
@@ -5455,7 +5477,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" s="7">
         <v>36116</v>
       </c>
@@ -5476,7 +5498,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
         <v>36341</v>
       </c>
@@ -5497,7 +5519,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
         <v>36396</v>
       </c>
@@ -5518,7 +5540,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
         <v>36480</v>
       </c>
@@ -5539,7 +5561,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" s="7">
         <v>36558</v>
       </c>
@@ -5560,7 +5582,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" s="7">
         <v>36606</v>
       </c>
@@ -5581,7 +5603,7 @@
         <v>5.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" s="7">
         <v>36662</v>
       </c>
@@ -5602,7 +5624,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
         <v>36894</v>
       </c>
@@ -5623,7 +5645,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
         <v>36922</v>
       </c>
@@ -5644,7 +5666,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" s="7">
         <v>36970</v>
       </c>
@@ -5665,7 +5687,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" s="7">
         <v>36999</v>
       </c>
@@ -5686,7 +5708,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" s="7">
         <v>37026</v>
       </c>
@@ -5707,7 +5729,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
         <v>37069</v>
       </c>
@@ -5728,7 +5750,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" s="7">
         <v>37124</v>
       </c>
@@ -5749,7 +5771,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" s="7">
         <v>37151</v>
       </c>
@@ -5770,7 +5792,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" s="7">
         <v>37166</v>
       </c>
@@ -5791,7 +5813,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
         <v>37201</v>
       </c>
@@ -5812,7 +5834,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" s="7">
         <v>37236</v>
       </c>
@@ -5833,7 +5855,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" s="7">
         <v>37566</v>
       </c>
@@ -5854,7 +5876,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" s="7">
         <v>37797</v>
       </c>
@@ -5875,7 +5897,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" s="7">
         <v>38168</v>
       </c>
@@ -5896,7 +5918,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" s="7">
         <v>38209</v>
       </c>
@@ -5917,7 +5939,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" s="7">
         <v>38251</v>
       </c>
@@ -5953,7 +5975,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" s="7">
         <v>38301</v>
       </c>
@@ -5974,7 +5996,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
         <v>38335</v>
       </c>
@@ -5995,7 +6017,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" s="7">
         <v>38385</v>
       </c>
@@ -6016,7 +6038,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" s="7">
         <v>38433</v>
       </c>
@@ -6037,7 +6059,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" s="7">
         <v>38475</v>
       </c>
@@ -6058,7 +6080,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
         <v>38533</v>
       </c>
@@ -6079,7 +6101,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" s="7">
         <v>38573</v>
       </c>
@@ -6100,7 +6122,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" s="7">
         <v>38615</v>
       </c>
@@ -6121,7 +6143,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" s="7">
         <v>38657</v>
       </c>
@@ -6142,7 +6164,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" s="7">
         <v>38699</v>
       </c>
@@ -6163,7 +6185,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" s="7">
         <v>38748</v>
       </c>
@@ -6184,7 +6206,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
         <v>38804</v>
       </c>
@@ -6205,7 +6227,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
         <v>38847</v>
       </c>
@@ -6226,7 +6248,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" s="7">
         <v>38897</v>
       </c>
@@ -6247,7 +6269,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="7">
         <v>39343</v>
       </c>
@@ -6268,7 +6290,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" s="7">
         <v>39386</v>
       </c>
@@ -6289,7 +6311,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
         <v>39427</v>
       </c>
@@ -6310,7 +6332,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" s="7">
         <v>39469</v>
       </c>
@@ -6331,7 +6353,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" s="7">
         <v>39477</v>
       </c>
@@ -6352,7 +6374,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" s="7">
         <v>39525</v>
       </c>
@@ -6376,7 +6398,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" s="7">
         <v>39568</v>
       </c>
@@ -6400,7 +6422,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" s="7">
         <v>39624</v>
       </c>
@@ -6424,7 +6446,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" s="7">
         <v>39665</v>
       </c>
@@ -6445,7 +6467,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" s="7">
         <v>39707</v>
       </c>
@@ -6469,7 +6491,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" s="7">
         <v>39729</v>
       </c>
@@ -6490,7 +6512,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" s="7">
         <v>39750</v>
       </c>
@@ -6514,7 +6536,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" s="7">
         <v>39798</v>
       </c>
@@ -6538,7 +6560,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" s="7">
         <v>39841</v>
       </c>
@@ -6562,7 +6584,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" s="7">
         <v>39890</v>
       </c>
@@ -6586,7 +6608,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" s="7">
         <v>39932</v>
       </c>
@@ -6610,7 +6632,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" s="7">
         <v>39988</v>
       </c>
@@ -6634,7 +6656,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" s="7">
         <v>40037</v>
       </c>
@@ -6658,7 +6680,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" s="7">
         <v>40079</v>
       </c>
@@ -6682,7 +6704,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" s="7">
         <v>40121</v>
       </c>
@@ -6706,7 +6728,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" s="7">
         <v>40163</v>
       </c>
@@ -6730,7 +6752,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" s="7">
         <v>40205</v>
       </c>
@@ -6754,7 +6776,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" s="7">
         <v>40253</v>
       </c>
@@ -6778,7 +6800,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" s="7">
         <v>40296</v>
       </c>
@@ -6802,7 +6824,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" s="7">
         <v>40352</v>
       </c>
@@ -6826,7 +6848,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" s="7">
         <v>40400</v>
       </c>
@@ -6850,7 +6872,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" s="7">
         <v>40442</v>
       </c>
@@ -6874,7 +6896,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" s="7">
         <v>40485</v>
       </c>
@@ -6898,7 +6920,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" s="7">
         <v>40526</v>
       </c>
@@ -6922,7 +6944,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" s="7">
         <v>40569</v>
       </c>
@@ -6946,7 +6968,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" s="7">
         <v>40617</v>
       </c>
@@ -6970,7 +6992,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" s="7">
         <v>40660</v>
       </c>
@@ -6994,7 +7016,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" s="7">
         <v>40716</v>
       </c>
@@ -7018,7 +7040,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" s="7">
         <v>40764</v>
       </c>
@@ -7042,7 +7064,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" s="7">
         <v>40807</v>
       </c>
@@ -7066,7 +7088,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" s="7">
         <v>40849</v>
       </c>
@@ -7090,7 +7112,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" s="7">
         <v>40890</v>
       </c>
@@ -7114,7 +7136,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" s="7">
         <v>40933</v>
       </c>
@@ -7138,7 +7160,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" s="7">
         <v>40981</v>
       </c>
@@ -7162,7 +7184,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" s="7">
         <v>41024</v>
       </c>
@@ -7186,7 +7208,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" s="7">
         <v>41080</v>
       </c>
@@ -7210,7 +7232,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" s="7">
         <v>41122</v>
       </c>
@@ -7234,7 +7256,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" s="7">
         <v>41165</v>
       </c>
@@ -7258,7 +7280,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" s="7">
         <v>41206</v>
       </c>
@@ -7282,7 +7304,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="7">
         <v>41255</v>
       </c>
@@ -7306,7 +7328,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" s="7">
         <v>41304</v>
       </c>
@@ -7330,7 +7352,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" s="7">
         <v>41353</v>
       </c>
@@ -7354,7 +7376,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" s="7">
         <v>41395</v>
       </c>
@@ -7378,7 +7400,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" s="7">
         <v>41444</v>
       </c>
@@ -7402,7 +7424,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" s="7">
         <v>41486</v>
       </c>
@@ -7441,7 +7463,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" s="7">
         <v>41535</v>
       </c>
@@ -7465,7 +7487,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" s="7">
         <v>41577</v>
       </c>
@@ -7489,7 +7511,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:7">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" s="7">
         <v>41626</v>
       </c>
@@ -7513,7 +7535,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="199" spans="1:7">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" s="7">
         <v>41668</v>
       </c>
@@ -7537,7 +7559,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="200" spans="1:7">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" s="7">
         <v>41717</v>
       </c>
@@ -7561,7 +7583,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="201" spans="1:7">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" s="7">
         <v>41759</v>
       </c>
@@ -7585,7 +7607,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="202" spans="1:7">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" s="7">
         <v>41808</v>
       </c>
@@ -7609,7 +7631,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" s="7">
         <v>41850</v>
       </c>
@@ -7633,7 +7655,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="204" spans="1:7">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" s="7">
         <v>41899</v>
       </c>
@@ -7657,7 +7679,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" s="7">
         <v>41941</v>
       </c>
@@ -7681,7 +7703,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" s="7">
         <v>41990</v>
       </c>
@@ -7705,7 +7727,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="207" spans="1:7">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" s="7">
         <v>42032</v>
       </c>
@@ -7729,7 +7751,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="1:7">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" s="7">
         <v>42081</v>
       </c>
@@ -7753,7 +7775,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:7">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" s="7">
         <v>42123</v>
       </c>
@@ -7777,7 +7799,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="210" spans="1:7">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" s="7">
         <v>42172</v>
       </c>
@@ -7801,7 +7823,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:7">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" s="7">
         <v>42214</v>
       </c>
@@ -7825,7 +7847,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="212" spans="1:7">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" s="7">
         <v>42264</v>
       </c>
@@ -7849,7 +7871,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="213" spans="1:7">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" s="7">
         <v>42305</v>
       </c>
@@ -7873,7 +7895,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="214" spans="1:7">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" s="7">
         <v>42354</v>
       </c>
@@ -7897,7 +7919,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="215" spans="1:7">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" s="7">
         <v>42396</v>
       </c>
@@ -7921,7 +7943,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:7">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" s="7">
         <v>42445</v>
       </c>
@@ -7945,7 +7967,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="217" spans="1:7">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" s="7">
         <v>42487</v>
       </c>
@@ -7969,7 +7991,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="218" spans="1:7">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" s="7">
         <v>42536</v>
       </c>
@@ -7993,7 +8015,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" s="7">
         <v>42578</v>
       </c>
@@ -8017,7 +8039,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="220" spans="1:7">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" s="7">
         <v>42634</v>
       </c>
@@ -8041,7 +8063,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="221" spans="1:7">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" s="7">
         <v>42676</v>
       </c>
@@ -8065,7 +8087,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" s="7">
         <v>42718</v>
       </c>
@@ -8089,7 +8111,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="223" spans="1:7">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" s="7">
         <v>42767</v>
       </c>
@@ -8113,7 +8135,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="224" spans="1:7">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" s="7">
         <v>42809</v>
       </c>
@@ -8137,7 +8159,7 @@
         <v>7.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" s="7">
         <v>42858</v>
       </c>
@@ -8161,7 +8183,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="226" spans="1:7">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" s="7">
         <v>42900</v>
       </c>
@@ -8185,7 +8207,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" s="7">
         <v>42942</v>
       </c>
@@ -8209,7 +8231,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" s="7">
         <v>42998</v>
       </c>
@@ -8233,7 +8255,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" s="7">
         <v>43040</v>
       </c>
@@ -8257,7 +8279,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" s="7">
         <v>43082</v>
       </c>
@@ -8281,7 +8303,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" s="7">
         <v>43131</v>
       </c>
@@ -8305,7 +8327,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" s="7">
         <v>43180</v>
       </c>
@@ -8329,7 +8351,7 @@
         <v>1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" s="7">
         <v>43222</v>
       </c>
@@ -8353,7 +8375,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" s="7">
         <v>43264</v>
       </c>
@@ -8377,7 +8399,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:7">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" s="7">
         <v>43313</v>
       </c>
@@ -8401,7 +8423,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="236" spans="1:7">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" s="7">
         <v>43369</v>
       </c>
@@ -8425,7 +8447,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="237" spans="1:7">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" s="7">
         <v>43412</v>
       </c>
@@ -8449,7 +8471,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" s="7">
         <v>43453</v>
       </c>
@@ -8473,7 +8495,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" s="7">
         <v>43495</v>
       </c>
@@ -8497,7 +8519,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" s="7">
         <v>43544</v>
       </c>
@@ -8521,7 +8543,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" s="7">
         <v>43586</v>
       </c>
@@ -8545,7 +8567,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" s="7">
         <v>43635</v>
       </c>
@@ -8569,7 +8591,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" s="7">
         <v>43677</v>
       </c>
@@ -8593,7 +8615,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" s="7">
         <v>43726</v>
       </c>
@@ -8617,7 +8639,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" s="7">
         <v>43768</v>
       </c>
@@ -8641,7 +8663,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" s="7">
         <v>43810</v>
       </c>
@@ -8665,7 +8687,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" s="7">
         <v>43859</v>
       </c>
@@ -8689,7 +8711,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" s="7">
         <v>43893</v>
       </c>
@@ -8710,7 +8732,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" s="7">
         <v>43905</v>
       </c>
@@ -8731,7 +8753,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" s="7">
         <v>43950</v>
       </c>
@@ -8755,7 +8777,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="251" spans="1:7">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" s="7">
         <v>43992</v>
       </c>
@@ -8779,7 +8801,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="252" spans="1:7">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" s="7">
         <v>44041</v>
       </c>
@@ -8803,7 +8825,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="253" spans="1:7">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" s="7">
         <v>44090</v>
       </c>
@@ -8827,7 +8849,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:7">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" s="7">
         <v>44140</v>
       </c>
@@ -8851,7 +8873,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="255" spans="1:7">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" s="7">
         <v>44181</v>
       </c>
@@ -8875,7 +8897,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="256" spans="1:7">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" s="7">
         <v>44223</v>
       </c>
@@ -8899,7 +8921,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="257" spans="1:7">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" s="7">
         <v>44272</v>
       </c>
@@ -8923,7 +8945,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="258" spans="1:7">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" s="7">
         <v>44314</v>
       </c>
@@ -8947,7 +8969,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="1:7">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" s="7">
         <v>44363</v>
       </c>
@@ -8986,7 +9008,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" s="7">
         <v>44405</v>
       </c>
@@ -9010,7 +9032,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="261" spans="1:7">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" s="7">
         <v>44461</v>
       </c>
@@ -9034,7 +9056,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="262" spans="1:7">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" s="7">
         <v>44503</v>
       </c>
@@ -9058,7 +9080,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="1:7">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" s="7">
         <v>44545</v>
       </c>
@@ -9082,7 +9104,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" s="7">
         <v>44587</v>
       </c>
@@ -9106,7 +9128,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="265" spans="1:7">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" s="7">
         <v>44636</v>
       </c>
@@ -9130,7 +9152,7 @@
         <v>2.5000000000000001E-3</v>
       </c>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" s="7">
         <v>44685</v>
       </c>
@@ -9154,7 +9176,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" s="7">
         <v>44727</v>
       </c>
@@ -9178,7 +9200,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="268" spans="1:7">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" s="7">
         <v>44769</v>
       </c>
@@ -9202,7 +9224,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" s="7">
         <v>44825</v>
       </c>
@@ -9226,7 +9248,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" s="7">
         <v>44867</v>
       </c>
@@ -9250,7 +9272,7 @@
         <v>3.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:7">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" s="7">
         <v>44909</v>
       </c>
@@ -9274,7 +9296,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="272" spans="1:7">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" s="7">
         <v>44958</v>
       </c>
@@ -9298,7 +9320,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="273" spans="1:7">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" s="7">
         <v>45007</v>
       </c>
@@ -9322,7 +9344,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="274" spans="1:7">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" s="7">
         <v>45049</v>
       </c>
@@ -9346,7 +9368,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="275" spans="1:7">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" s="7">
         <v>45091</v>
       </c>
@@ -9370,7 +9392,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:7">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" s="7">
         <v>45133</v>
       </c>
@@ -9394,7 +9416,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="277" spans="1:7">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" s="7">
         <v>45189</v>
       </c>
@@ -9418,7 +9440,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="278" spans="1:7">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" s="7">
         <v>45231</v>
       </c>
@@ -9442,7 +9464,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:7">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" s="7">
         <v>45273</v>
       </c>
@@ -9466,7 +9488,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="280" spans="1:7">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" s="7">
         <v>45322</v>
       </c>
@@ -9490,7 +9512,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:7">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" s="7">
         <v>45371</v>
       </c>
@@ -9514,7 +9536,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" s="7">
         <v>45413</v>
       </c>
@@ -9538,7 +9560,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="283" spans="1:7">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" s="7">
         <v>45455</v>
       </c>
@@ -9562,7 +9584,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" s="7">
         <v>45504</v>
       </c>
@@ -9586,7 +9608,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" s="7">
         <v>45553</v>
       </c>
@@ -9610,7 +9632,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:7">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" s="7">
         <v>45603</v>
       </c>
@@ -9634,7 +9656,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" s="7">
         <v>45644</v>
       </c>
@@ -9658,7 +9680,7 @@
         <v>4.7500000000000001E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" s="7">
         <v>45686</v>
       </c>
@@ -9682,7 +9704,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" s="7">
         <v>45735</v>
       </c>
@@ -9706,7 +9728,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="290" spans="1:7">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" s="7">
         <v>45784</v>
       </c>
@@ -9730,7 +9752,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="291" spans="1:7">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" s="7">
         <v>45826</v>
       </c>
@@ -9754,7 +9776,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" s="7">
         <v>45868</v>
       </c>
@@ -9778,7 +9800,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="293" spans="1:7">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" s="7">
         <v>45917</v>
       </c>
@@ -9802,7 +9824,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" s="7">
         <v>45959</v>
       </c>
@@ -9826,7 +9848,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="295" spans="1:7">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" s="7">
         <v>46001</v>
       </c>
@@ -9850,7 +9872,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" s="7">
         <v>46050</v>
       </c>
@@ -9889,7 +9911,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" s="7">
         <v>46099</v>
       </c>
@@ -9913,7 +9935,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" s="7">
         <v>46141</v>
       </c>
@@ -9937,7 +9959,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" s="7">
         <v>46190</v>
       </c>
@@ -9976,7 +9998,7 @@
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="300" spans="1:7">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" s="7">
         <v>46232</v>
       </c>
@@ -9990,11 +10012,17 @@
         <f t="shared" si="6"/>
         <v>UTC-4</v>
       </c>
+      <c r="E300" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="F300" s="10">
+        <v>3.7499999999999999E-2</v>
+      </c>
       <c r="G300" s="10">
         <v>3.7499999999999999E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" s="7">
         <v>46281</v>
       </c>
@@ -10009,7 +10037,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="302" spans="1:7">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" s="7">
         <v>46323</v>
       </c>
@@ -10024,7 +10052,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="303" spans="1:7">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" s="7">
         <v>46365</v>
       </c>
@@ -10039,7 +10067,7 @@
         <v>UTC-5</v>
       </c>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" s="7">
         <v>46414</v>
       </c>
@@ -10054,7 +10082,7 @@
         <v>UTC-5</v>
       </c>
     </row>
-    <row r="305" spans="1:4">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" s="7">
         <v>46463</v>
       </c>
@@ -10084,7 +10112,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="306" spans="1:4">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" s="7">
         <v>46140</v>
       </c>
@@ -10099,7 +10127,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="307" spans="1:4">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" s="7">
         <v>46547</v>
       </c>
@@ -10114,7 +10142,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="308" spans="1:4">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" s="7">
         <v>46596</v>
       </c>
@@ -10129,7 +10157,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="309" spans="1:4">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="7">
         <v>46645</v>
       </c>
@@ -10144,7 +10172,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="310" spans="1:4">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="7">
         <v>46687</v>
       </c>
@@ -10159,7 +10187,7 @@
         <v>UTC-4</v>
       </c>
     </row>
-    <row r="311" spans="1:4">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" s="7">
         <v>46729</v>
       </c>
@@ -10184,7 +10212,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9EAB5-0149-4548-96A8-B9F3C1083AD8}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10195,12 +10223,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3E03F4A-9B60-4F24-A253-F9B33163B43A}">
   <dimension ref="B2:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>

--- a/data_lake/macro/USA/FED Target Rate.xlsx
+++ b/data_lake/macro/USA/FED Target Rate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9823834-A5F1-4581-A1B9-8A87B217AB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FDA18D1-76B1-46F8-B706-DFE5518E8E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fed Target Rate" sheetId="1" r:id="rId1"/>
